--- a/members.xlsx
+++ b/members.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yoich\OneDrive\デスクトップ\卓球\台割？\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FACAB0A-1839-460A-8657-2F1ADAF306DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE727E02-7823-4AD5-8343-ED958865B707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="79">
   <si>
     <t>中山</t>
   </si>
@@ -235,13 +235,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>中村</t>
-    <rPh sb="0" eb="2">
-      <t>ナカムラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>水田</t>
     <rPh sb="0" eb="2">
       <t>ミズタ</t>
@@ -432,7 +425,42 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>瀬口</t>
+    <rPh sb="0" eb="2">
+      <t>セグチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中村亘</t>
+    <rPh sb="0" eb="2">
+      <t>ナカムラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ワタリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中村望</t>
+    <rPh sb="0" eb="2">
+      <t>ナカムラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ノゾム</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -766,35 +794,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" t="s">
         <v>68</v>
       </c>
-      <c r="B1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>69</v>
-      </c>
-      <c r="D1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -805,38 +833,38 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4">
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B5">
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -847,10 +875,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -861,10 +889,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -875,10 +903,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -889,10 +917,10 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -903,10 +931,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -917,10 +945,10 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -931,287 +959,278 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="B13">
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B14">
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="B16">
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B18">
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B21">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B23">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B25">
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B26">
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="B31">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>59</v>
-      </c>
-      <c r="D31" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D32" t="s">
         <v>60</v>
@@ -1219,443 +1238,432 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B33">
         <v>5</v>
       </c>
       <c r="C33" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" t="s">
         <v>59</v>
-      </c>
-      <c r="D33" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B34">
         <v>5</v>
       </c>
       <c r="C34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" t="s">
         <v>59</v>
-      </c>
-      <c r="D34" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B35">
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B36">
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B37">
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="1" t="s">
-        <v>42</v>
+      <c r="A38" t="s">
+        <v>40</v>
       </c>
       <c r="B38">
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" t="s">
-        <v>44</v>
+      <c r="A39" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D39" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B40">
         <v>4</v>
       </c>
       <c r="C40" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" t="s">
         <v>59</v>
-      </c>
-      <c r="D40" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B41">
         <v>4</v>
       </c>
       <c r="C41" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" t="s">
         <v>59</v>
-      </c>
-      <c r="D41" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="B42">
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B43">
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="B44">
         <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B45">
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B46">
         <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D46" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>59</v>
-      </c>
-      <c r="D47" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D49" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D50" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B51">
         <v>3</v>
       </c>
       <c r="C51" t="s">
-        <v>59</v>
-      </c>
-      <c r="D51" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B52">
         <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>59</v>
-      </c>
-      <c r="D52" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>59</v>
-      </c>
-      <c r="D53" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>59</v>
-      </c>
-      <c r="D54" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D55" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B56">
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D56" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D57" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>59</v>
-      </c>
-      <c r="D58" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>59</v>
-      </c>
-      <c r="D59" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>59</v>
-      </c>
-      <c r="D60" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>59</v>
-      </c>
-      <c r="D61" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>59</v>
-      </c>
-      <c r="D62" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>59</v>
-      </c>
-      <c r="D63" t="s">
-        <v>74</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>49</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>52</v>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D64">
-    <sortCondition descending="1" ref="C2:C64"/>
-    <sortCondition descending="1" ref="B2:B64"/>
-    <sortCondition ref="D2:D64"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D66">
+    <sortCondition descending="1" ref="C2:C66"/>
+    <sortCondition descending="1" ref="B2:B66"/>
+    <sortCondition ref="D2:D66"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/members.xlsx
+++ b/members.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yoich\OneDrive\デスクトップ\卓球\台割？\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yoich\OneDrive\デスクトップ\卓球\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE727E02-7823-4AD5-8343-ED958865B707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37185A5A-C008-4FB2-B33E-1E93A1D6D5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="67">
   <si>
     <t>中山</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>内泉</t>
-  </si>
-  <si>
-    <t>塩貝</t>
   </si>
   <si>
     <t>工藤</t>
@@ -97,9 +94,6 @@
     <t>城戸</t>
   </si>
   <si>
-    <t>森岡</t>
-  </si>
-  <si>
     <t>稲田</t>
   </si>
   <si>
@@ -176,16 +170,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>新原</t>
-    <rPh sb="0" eb="1">
-      <t>シン</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>ハラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>喜多</t>
     <rPh sb="0" eb="2">
       <t>キタ</t>
@@ -214,23 +198,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>岸野</t>
-    <rPh sb="0" eb="2">
-      <t>キシノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>安東</t>
     <rPh sb="0" eb="2">
       <t>アンドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>市村</t>
-    <rPh sb="0" eb="2">
-      <t>イチムラ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -280,13 +250,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>好本</t>
-    <rPh sb="0" eb="2">
-      <t>ヨシモト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>竹田</t>
     <rPh sb="0" eb="2">
       <t>タケダ</t>
@@ -294,13 +257,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>荒木</t>
-    <rPh sb="0" eb="2">
-      <t>アラキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>長内</t>
     <rPh sb="0" eb="2">
       <t>ナガウチ</t>
@@ -336,13 +292,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>寺田</t>
-    <rPh sb="0" eb="2">
-      <t>テラダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>M</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -368,16 +317,6 @@
   </si>
   <si>
     <t>E</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>福田弥</t>
-    <rPh sb="0" eb="2">
-      <t>フクダ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ヤ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -387,13 +326,6 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>橋本</t>
-    <rPh sb="0" eb="2">
-      <t>ハシモト</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -422,17 +354,6 @@
   </si>
   <si>
     <t>E</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>瀬口</t>
-    <rPh sb="0" eb="2">
-      <t>セグチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>F</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -794,35 +715,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -833,435 +754,435 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B4">
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>71</v>
+      <c r="A5" t="s">
+        <v>1</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B13">
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="B14">
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B16">
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B21">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B23">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>49</v>
+      </c>
+      <c r="D26" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>49</v>
+      </c>
+      <c r="D27" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D29" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>50</v>
+      </c>
+      <c r="D31" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="B32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D32" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B33">
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D33" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B34">
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D34" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1272,24 +1193,24 @@
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>32</v>
+      <c r="A36" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B36">
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1297,373 +1218,234 @@
         <v>38</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D37" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
         <v>40</v>
       </c>
-      <c r="B38">
-        <v>5</v>
-      </c>
-      <c r="C38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="B39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B40">
         <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B41">
         <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>58</v>
-      </c>
-      <c r="D41" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>58</v>
-      </c>
-      <c r="D45" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>58</v>
-      </c>
-      <c r="D46" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
+        <v>50</v>
+      </c>
+      <c r="D47" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D49" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>58</v>
-      </c>
-      <c r="D50" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" t="s">
-        <v>47</v>
-      </c>
-      <c r="B55">
-        <v>2</v>
-      </c>
-      <c r="C55" t="s">
-        <v>58</v>
-      </c>
-      <c r="D55" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" t="s">
-        <v>27</v>
-      </c>
-      <c r="B56">
-        <v>2</v>
-      </c>
-      <c r="C56" t="s">
-        <v>58</v>
-      </c>
-      <c r="D56" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" t="s">
-        <v>51</v>
-      </c>
-      <c r="B57">
-        <v>2</v>
-      </c>
-      <c r="C57" t="s">
-        <v>58</v>
-      </c>
-      <c r="D57" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" t="s">
-        <v>50</v>
-      </c>
-      <c r="B58">
-        <v>2</v>
-      </c>
-      <c r="C58" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" t="s">
-        <v>31</v>
-      </c>
-      <c r="B59">
-        <v>2</v>
-      </c>
-      <c r="C59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" t="s">
-        <v>35</v>
-      </c>
-      <c r="B60">
-        <v>2</v>
-      </c>
-      <c r="C60" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
-      </c>
-      <c r="C61" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
-      </c>
-      <c r="C62" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
-      </c>
-      <c r="C63" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" t="s">
-        <v>49</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
-      </c>
-      <c r="C64" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" t="s">
-        <v>52</v>
-      </c>
-      <c r="B65">
-        <v>2</v>
-      </c>
-      <c r="C65" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D66">
-    <sortCondition descending="1" ref="C2:C66"/>
-    <sortCondition descending="1" ref="B2:B66"/>
-    <sortCondition ref="D2:D66"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D55">
+    <sortCondition descending="1" ref="C2:C55"/>
+    <sortCondition descending="1" ref="B2:B55"/>
+    <sortCondition ref="D2:D55"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
